--- a/artfynd/A 28993-2022 artfynd.xlsx
+++ b/artfynd/A 28993-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121569599</v>
+        <v>121569597</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641452</v>
+        <v>641379</v>
       </c>
       <c r="R2" t="n">
-        <v>7165641</v>
+        <v>7165675</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121569597</v>
+        <v>121569600</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>641379</v>
+        <v>641503</v>
       </c>
       <c r="R3" t="n">
-        <v>7165675</v>
+        <v>7165604</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569595</v>
+        <v>121569605</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>641451</v>
+        <v>641625</v>
       </c>
       <c r="R4" t="n">
-        <v>7165761</v>
+        <v>7165454</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569603</v>
+        <v>121569601</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>90738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>641518</v>
+        <v>641504</v>
       </c>
       <c r="R5" t="n">
-        <v>7165556</v>
+        <v>7165598</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121569604</v>
+        <v>121569596</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
+        <v>90720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>641620</v>
+        <v>641373</v>
       </c>
       <c r="R6" t="n">
-        <v>7165480</v>
+        <v>7165681</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569596</v>
+        <v>121569602</v>
       </c>
       <c r="B7" t="n">
-        <v>90719</v>
+        <v>90738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>641373</v>
+        <v>641514</v>
       </c>
       <c r="R7" t="n">
-        <v>7165681</v>
+        <v>7165572</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569605</v>
+        <v>121569603</v>
       </c>
       <c r="B8" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>641625</v>
+        <v>641518</v>
       </c>
       <c r="R8" t="n">
-        <v>7165454</v>
+        <v>7165556</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569600</v>
+        <v>121569598</v>
       </c>
       <c r="B9" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>641503</v>
+        <v>641399</v>
       </c>
       <c r="R9" t="n">
-        <v>7165604</v>
+        <v>7165664</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569594</v>
+        <v>121569595</v>
       </c>
       <c r="B10" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>641501</v>
+        <v>641451</v>
       </c>
       <c r="R10" t="n">
-        <v>7165772</v>
+        <v>7165761</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569601</v>
+        <v>121569604</v>
       </c>
       <c r="B11" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>641504</v>
+        <v>641620</v>
       </c>
       <c r="R11" t="n">
-        <v>7165598</v>
+        <v>7165480</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121569602</v>
+        <v>121569594</v>
       </c>
       <c r="B12" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>641514</v>
+        <v>641501</v>
       </c>
       <c r="R12" t="n">
-        <v>7165572</v>
+        <v>7165772</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121569598</v>
+        <v>121569599</v>
       </c>
       <c r="B13" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>641399</v>
+        <v>641452</v>
       </c>
       <c r="R13" t="n">
-        <v>7165664</v>
+        <v>7165641</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 28993-2022 artfynd.xlsx
+++ b/artfynd/A 28993-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121569597</v>
+        <v>121569602</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641379</v>
+        <v>641514</v>
       </c>
       <c r="R2" t="n">
-        <v>7165675</v>
+        <v>7165572</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121569600</v>
+        <v>121569598</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>641503</v>
+        <v>641399</v>
       </c>
       <c r="R3" t="n">
-        <v>7165604</v>
+        <v>7165664</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569605</v>
+        <v>121569597</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>641625</v>
+        <v>641379</v>
       </c>
       <c r="R4" t="n">
-        <v>7165454</v>
+        <v>7165675</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569601</v>
+        <v>121569599</v>
       </c>
       <c r="B5" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>641504</v>
+        <v>641452</v>
       </c>
       <c r="R5" t="n">
-        <v>7165598</v>
+        <v>7165641</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121569596</v>
+        <v>121569605</v>
       </c>
       <c r="B6" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>641373</v>
+        <v>641625</v>
       </c>
       <c r="R6" t="n">
-        <v>7165681</v>
+        <v>7165454</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569602</v>
+        <v>121569600</v>
       </c>
       <c r="B7" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>641514</v>
+        <v>641503</v>
       </c>
       <c r="R7" t="n">
-        <v>7165572</v>
+        <v>7165604</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569603</v>
+        <v>121569601</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>641518</v>
+        <v>641504</v>
       </c>
       <c r="R8" t="n">
-        <v>7165556</v>
+        <v>7165598</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569598</v>
+        <v>121569603</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>641399</v>
+        <v>641518</v>
       </c>
       <c r="R9" t="n">
-        <v>7165664</v>
+        <v>7165556</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569595</v>
+        <v>121569604</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>641451</v>
+        <v>641620</v>
       </c>
       <c r="R10" t="n">
-        <v>7165761</v>
+        <v>7165480</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569604</v>
+        <v>121569595</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>641620</v>
+        <v>641451</v>
       </c>
       <c r="R11" t="n">
-        <v>7165480</v>
+        <v>7165761</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121569599</v>
+        <v>121569596</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>641452</v>
+        <v>641373</v>
       </c>
       <c r="R13" t="n">
-        <v>7165641</v>
+        <v>7165681</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 28993-2022 artfynd.xlsx
+++ b/artfynd/A 28993-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121569602</v>
+        <v>121569605</v>
       </c>
       <c r="B2" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641514</v>
+        <v>641625</v>
       </c>
       <c r="R2" t="n">
-        <v>7165572</v>
+        <v>7165454</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121569598</v>
+        <v>121569594</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>641399</v>
+        <v>641501</v>
       </c>
       <c r="R3" t="n">
-        <v>7165664</v>
+        <v>7165772</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569597</v>
+        <v>121569601</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>641379</v>
+        <v>641504</v>
       </c>
       <c r="R4" t="n">
-        <v>7165675</v>
+        <v>7165598</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569599</v>
+        <v>121569603</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>641452</v>
+        <v>641518</v>
       </c>
       <c r="R5" t="n">
-        <v>7165641</v>
+        <v>7165556</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121569605</v>
+        <v>121569599</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>641625</v>
+        <v>641452</v>
       </c>
       <c r="R6" t="n">
-        <v>7165454</v>
+        <v>7165641</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569600</v>
+        <v>121569602</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>641503</v>
+        <v>641514</v>
       </c>
       <c r="R7" t="n">
-        <v>7165604</v>
+        <v>7165572</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569601</v>
+        <v>121569596</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>641504</v>
+        <v>641373</v>
       </c>
       <c r="R8" t="n">
-        <v>7165598</v>
+        <v>7165681</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569603</v>
+        <v>121569595</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>641518</v>
+        <v>641451</v>
       </c>
       <c r="R9" t="n">
-        <v>7165556</v>
+        <v>7165761</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569604</v>
+        <v>121569598</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>641620</v>
+        <v>641399</v>
       </c>
       <c r="R10" t="n">
-        <v>7165480</v>
+        <v>7165664</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569595</v>
+        <v>121569597</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>641451</v>
+        <v>641379</v>
       </c>
       <c r="R11" t="n">
-        <v>7165761</v>
+        <v>7165675</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121569594</v>
+        <v>121569600</v>
       </c>
       <c r="B12" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>641501</v>
+        <v>641503</v>
       </c>
       <c r="R12" t="n">
-        <v>7165772</v>
+        <v>7165604</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121569596</v>
+        <v>121569604</v>
       </c>
       <c r="B13" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>641373</v>
+        <v>641620</v>
       </c>
       <c r="R13" t="n">
-        <v>7165681</v>
+        <v>7165480</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 28993-2022 artfynd.xlsx
+++ b/artfynd/A 28993-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121569605</v>
+        <v>121569595</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641625</v>
+        <v>641451</v>
       </c>
       <c r="R2" t="n">
-        <v>7165454</v>
+        <v>7165761</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121569594</v>
+        <v>121569599</v>
       </c>
       <c r="B3" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>641501</v>
+        <v>641452</v>
       </c>
       <c r="R3" t="n">
-        <v>7165772</v>
+        <v>7165641</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569601</v>
+        <v>121569600</v>
       </c>
       <c r="B4" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>641504</v>
+        <v>641503</v>
       </c>
       <c r="R4" t="n">
-        <v>7165598</v>
+        <v>7165604</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569603</v>
+        <v>121569602</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>641518</v>
+        <v>641514</v>
       </c>
       <c r="R5" t="n">
-        <v>7165556</v>
+        <v>7165572</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121569599</v>
+        <v>121569603</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>641452</v>
+        <v>641518</v>
       </c>
       <c r="R6" t="n">
-        <v>7165641</v>
+        <v>7165556</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569602</v>
+        <v>121569596</v>
       </c>
       <c r="B7" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>641514</v>
+        <v>641373</v>
       </c>
       <c r="R7" t="n">
-        <v>7165572</v>
+        <v>7165681</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569596</v>
+        <v>121569601</v>
       </c>
       <c r="B8" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>641373</v>
+        <v>641504</v>
       </c>
       <c r="R8" t="n">
-        <v>7165681</v>
+        <v>7165598</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569595</v>
+        <v>121569605</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>641451</v>
+        <v>641625</v>
       </c>
       <c r="R9" t="n">
-        <v>7165761</v>
+        <v>7165454</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569598</v>
+        <v>121569604</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>641399</v>
+        <v>641620</v>
       </c>
       <c r="R10" t="n">
-        <v>7165664</v>
+        <v>7165480</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121569600</v>
+        <v>121569594</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>641503</v>
+        <v>641501</v>
       </c>
       <c r="R12" t="n">
-        <v>7165604</v>
+        <v>7165772</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121569604</v>
+        <v>121569598</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>641620</v>
+        <v>641399</v>
       </c>
       <c r="R13" t="n">
-        <v>7165480</v>
+        <v>7165664</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 28993-2022 artfynd.xlsx
+++ b/artfynd/A 28993-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121569595</v>
+        <v>121569600</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641451</v>
+        <v>641503</v>
       </c>
       <c r="R2" t="n">
-        <v>7165761</v>
+        <v>7165604</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121569599</v>
+        <v>121569597</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>641452</v>
+        <v>641379</v>
       </c>
       <c r="R3" t="n">
-        <v>7165641</v>
+        <v>7165675</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569600</v>
+        <v>121569594</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>90746</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>641503</v>
+        <v>641501</v>
       </c>
       <c r="R4" t="n">
-        <v>7165604</v>
+        <v>7165772</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569602</v>
+        <v>121569603</v>
       </c>
       <c r="B5" t="n">
-        <v>90738</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>641514</v>
+        <v>641518</v>
       </c>
       <c r="R5" t="n">
-        <v>7165572</v>
+        <v>7165556</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121569603</v>
+        <v>121569602</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>90746</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>641518</v>
+        <v>641514</v>
       </c>
       <c r="R6" t="n">
-        <v>7165556</v>
+        <v>7165572</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569596</v>
+        <v>121569605</v>
       </c>
       <c r="B7" t="n">
-        <v>90720</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>641373</v>
+        <v>641625</v>
       </c>
       <c r="R7" t="n">
-        <v>7165681</v>
+        <v>7165454</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569601</v>
+        <v>121569595</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>641504</v>
+        <v>641451</v>
       </c>
       <c r="R8" t="n">
-        <v>7165598</v>
+        <v>7165761</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569605</v>
+        <v>121569598</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>641625</v>
+        <v>641399</v>
       </c>
       <c r="R9" t="n">
-        <v>7165454</v>
+        <v>7165664</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569604</v>
+        <v>121569599</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>641620</v>
+        <v>641452</v>
       </c>
       <c r="R10" t="n">
-        <v>7165480</v>
+        <v>7165641</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569597</v>
+        <v>121569604</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>641379</v>
+        <v>641620</v>
       </c>
       <c r="R11" t="n">
-        <v>7165675</v>
+        <v>7165480</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121569594</v>
+        <v>121569601</v>
       </c>
       <c r="B12" t="n">
-        <v>90738</v>
+        <v>90746</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>641501</v>
+        <v>641504</v>
       </c>
       <c r="R12" t="n">
-        <v>7165772</v>
+        <v>7165598</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121569598</v>
+        <v>121569596</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>90728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>641399</v>
+        <v>641373</v>
       </c>
       <c r="R13" t="n">
-        <v>7165664</v>
+        <v>7165681</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 28993-2022 artfynd.xlsx
+++ b/artfynd/A 28993-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121569597</v>
+        <v>121569603</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641379</v>
+        <v>641518</v>
       </c>
       <c r="R2" t="n">
-        <v>7165675</v>
+        <v>7165556</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121569605</v>
+        <v>121569598</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>641625</v>
+        <v>641399</v>
       </c>
       <c r="R3" t="n">
-        <v>7165454</v>
+        <v>7165664</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569595</v>
+        <v>121569596</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>641451</v>
+        <v>641373</v>
       </c>
       <c r="R4" t="n">
-        <v>7165761</v>
+        <v>7165681</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569601</v>
+        <v>121569599</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>641504</v>
+        <v>641452</v>
       </c>
       <c r="R5" t="n">
-        <v>7165598</v>
+        <v>7165641</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121569604</v>
+        <v>121569595</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>641620</v>
+        <v>641451</v>
       </c>
       <c r="R6" t="n">
-        <v>7165480</v>
+        <v>7165761</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569594</v>
+        <v>121569604</v>
       </c>
       <c r="B7" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>641501</v>
+        <v>641620</v>
       </c>
       <c r="R7" t="n">
-        <v>7165772</v>
+        <v>7165480</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569600</v>
+        <v>121569602</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>641503</v>
+        <v>641514</v>
       </c>
       <c r="R8" t="n">
-        <v>7165604</v>
+        <v>7165572</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569599</v>
+        <v>121569600</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>641452</v>
+        <v>641503</v>
       </c>
       <c r="R9" t="n">
-        <v>7165641</v>
+        <v>7165604</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569602</v>
+        <v>121569597</v>
       </c>
       <c r="B10" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>641514</v>
+        <v>641379</v>
       </c>
       <c r="R10" t="n">
-        <v>7165572</v>
+        <v>7165675</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569596</v>
+        <v>121569601</v>
       </c>
       <c r="B11" t="n">
-        <v>90728</v>
+        <v>90746</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>641373</v>
+        <v>641504</v>
       </c>
       <c r="R11" t="n">
-        <v>7165681</v>
+        <v>7165598</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121569598</v>
+        <v>121569594</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>641399</v>
+        <v>641501</v>
       </c>
       <c r="R12" t="n">
-        <v>7165664</v>
+        <v>7165772</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121569603</v>
+        <v>121569605</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>641518</v>
+        <v>641625</v>
       </c>
       <c r="R13" t="n">
-        <v>7165556</v>
+        <v>7165454</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 28993-2022 artfynd.xlsx
+++ b/artfynd/A 28993-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121569603</v>
+        <v>121569594</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641518</v>
+        <v>641501</v>
       </c>
       <c r="R2" t="n">
-        <v>7165556</v>
+        <v>7165772</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121569598</v>
+        <v>121569600</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>641399</v>
+        <v>641503</v>
       </c>
       <c r="R3" t="n">
-        <v>7165664</v>
+        <v>7165604</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569596</v>
+        <v>121569597</v>
       </c>
       <c r="B4" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>641373</v>
+        <v>641379</v>
       </c>
       <c r="R4" t="n">
-        <v>7165681</v>
+        <v>7165675</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569599</v>
+        <v>121569601</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>641452</v>
+        <v>641504</v>
       </c>
       <c r="R5" t="n">
-        <v>7165641</v>
+        <v>7165598</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569604</v>
+        <v>121569602</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>641620</v>
+        <v>641514</v>
       </c>
       <c r="R7" t="n">
-        <v>7165480</v>
+        <v>7165572</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569602</v>
+        <v>121569596</v>
       </c>
       <c r="B8" t="n">
-        <v>90746</v>
+        <v>90728</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>641514</v>
+        <v>641373</v>
       </c>
       <c r="R8" t="n">
-        <v>7165572</v>
+        <v>7165681</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569600</v>
+        <v>121569599</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>641503</v>
+        <v>641452</v>
       </c>
       <c r="R9" t="n">
-        <v>7165604</v>
+        <v>7165641</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569597</v>
+        <v>121569603</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>641379</v>
+        <v>641518</v>
       </c>
       <c r="R10" t="n">
-        <v>7165675</v>
+        <v>7165556</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569601</v>
+        <v>121569598</v>
       </c>
       <c r="B11" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>641504</v>
+        <v>641399</v>
       </c>
       <c r="R11" t="n">
-        <v>7165598</v>
+        <v>7165664</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121569594</v>
+        <v>121569604</v>
       </c>
       <c r="B12" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>641501</v>
+        <v>641620</v>
       </c>
       <c r="R12" t="n">
-        <v>7165772</v>
+        <v>7165480</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
